--- a/artfynd/A 62671-2019 artfynd.xlsx
+++ b/artfynd/A 62671-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62671-2019 artfynd.xlsx
+++ b/artfynd/A 62671-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,228 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115137137</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105200</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Badelunda NVI, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593857</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6612043</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115137138</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101850</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Badelunda NVI, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>593856</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6612053</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
